--- a/results/phi4_14b/comparison_ToTPlainLLM/ToTPlainLLM_evaluated.xlsx
+++ b/results/phi4_14b/comparison_ToTPlainLLM/ToTPlainLLM_evaluated.xlsx
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1884057928956628</v>
+        <v>0.1661721019306326</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008504017423071724</v>
+        <v>6.689237336457705e-79</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5976510643959045</v>
+        <v>0.605306088924408</v>
       </c>
       <c r="F2" t="n">
-        <v>26.30083333333334</v>
+        <v>15.73544403330251</v>
       </c>
       <c r="G2" t="n">
-        <v>0.510879848628193</v>
+        <v>0.847682119205298</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -529,13 +529,13 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2227979274611399</v>
+        <v>0.4674556213017752</v>
       </c>
     </row>
     <row r="3">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07947019743870884</v>
+        <v>0.09677419206555671</v>
       </c>
       <c r="D3" t="n">
-        <v>7.053721699186672e-232</v>
+        <v>7.873430974476304e-232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4320713877677917</v>
+        <v>0.472367912530899</v>
       </c>
       <c r="F3" t="n">
-        <v>47.64178846153848</v>
+        <v>11.71612423312882</v>
       </c>
       <c r="G3" t="n">
-        <v>7.981651376146789</v>
+        <v>6.26605504587156</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.28</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="4">
@@ -591,37 +591,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1959183627208664</v>
+        <v>0.2508960524176206</v>
       </c>
       <c r="D4" t="n">
-        <v>7.506202263513344e-156</v>
+        <v>6.055714513253697e-79</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6249730587005615</v>
+        <v>0.5730676054954529</v>
       </c>
       <c r="F4" t="n">
-        <v>30.95500000000001</v>
+        <v>31.2165092918132</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.7467948717948718</v>
       </c>
       <c r="H4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.5</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3827160493827161</v>
       </c>
     </row>
     <row r="5">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1870503562866829</v>
+        <v>0.403314912324868</v>
       </c>
       <c r="D5" t="n">
-        <v>1.739456386435759e-80</v>
+        <v>0.1334659684810689</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6157004237174988</v>
+        <v>0.6655306220054626</v>
       </c>
       <c r="F5" t="n">
-        <v>29.33764705882356</v>
+        <v>42.10199485199487</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3142389525368249</v>
+        <v>0.7119476268412439</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.494949494949495</v>
       </c>
     </row>
     <row r="6">
@@ -677,22 +677,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4367816043311167</v>
+        <v>0.3768115892543584</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1029075740018544</v>
+        <v>1.150212811341066e-78</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6816045641899109</v>
+        <v>0.6593446135520935</v>
       </c>
       <c r="F6" t="n">
-        <v>49.42148809523809</v>
+        <v>41.50961538461542</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7172413793103448</v>
+        <v>0.8804597701149425</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -701,13 +701,13 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.2792792792792793</v>
       </c>
     </row>
     <row r="7">
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3277693436973756</v>
+        <v>0.2342606108923469</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01898641880084134</v>
+        <v>0.002238467314476</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6669158339500427</v>
+        <v>0.6392207145690918</v>
       </c>
       <c r="F7" t="n">
-        <v>41.07818629590378</v>
+        <v>27.01716221033868</v>
       </c>
       <c r="G7" t="n">
-        <v>0.330811754437009</v>
+        <v>0.3549607215594995</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1176470588235294</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -744,13 +744,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7183098591549296</v>
+        <v>0.6581196581196581</v>
       </c>
     </row>
     <row r="8">
@@ -763,35 +763,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.1761363590728307</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1.801897236458547e-79</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3380750119686127</v>
+        <v>0.6301587224006653</v>
       </c>
       <c r="F8" t="n">
-        <v>12.42500000000001</v>
+        <v>32.11366666666669</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04930555555555555</v>
+        <v>0.5375</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2741935483870968</v>
       </c>
     </row>
     <row r="9">
@@ -804,35 +806,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006993006649469429</v>
+        <v>0.1727019464594471</v>
       </c>
       <c r="D9" t="n">
-        <v>4.626996437597695e-283</v>
+        <v>3.189002020962334e-157</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3232589066028595</v>
+        <v>0.6524112820625305</v>
       </c>
       <c r="F9" t="n">
-        <v>12.42500000000001</v>
+        <v>45.353269428278</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04113557358053303</v>
+        <v>0.3215527230590962</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
@@ -845,35 +849,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.2339832824574608</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1.851298572308437e-79</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3234608471393585</v>
+        <v>0.6334545016288757</v>
       </c>
       <c r="F10" t="n">
-        <v>12.42500000000001</v>
+        <v>35.57582730923698</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04695767195767196</v>
+        <v>0.4748677248677249</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="11">
@@ -886,35 +892,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006756756424625656</v>
+        <v>0.2679425795017285</v>
       </c>
       <c r="D11" t="n">
-        <v>3.199290466293744e-295</v>
+        <v>1.373332135069192e-79</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3082520365715027</v>
+        <v>0.6647945642471313</v>
       </c>
       <c r="F11" t="n">
-        <v>12.42500000000001</v>
+        <v>60.05026575183612</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03881902679059596</v>
+        <v>0.4248223072717332</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4594594594594594</v>
       </c>
     </row>
     <row r="12">
@@ -927,35 +935,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.2176165763503719</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.003825427406179127</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3188543021678925</v>
+        <v>0.6445428133010864</v>
       </c>
       <c r="F12" t="n">
-        <v>12.42500000000001</v>
+        <v>40.86903374233131</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04043280182232346</v>
+        <v>0.3861047835990888</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2424242424242424</v>
       </c>
     </row>
     <row r="13">
@@ -968,35 +978,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.006644517945718055</v>
+        <v>0.2355555510534321</v>
       </c>
       <c r="D13" t="n">
-        <v>1.737745674680046e-291</v>
+        <v>0.006194512670275375</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3241649270057678</v>
+        <v>0.5915787816047668</v>
       </c>
       <c r="F13" t="n">
-        <v>12.42500000000001</v>
+        <v>43.71379284649777</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0393569844789357</v>
+        <v>0.5182926829268293</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3798449612403101</v>
       </c>
     </row>
     <row r="14">
@@ -1009,35 +1021,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.2205882311827183</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.003493881194384704</v>
       </c>
       <c r="E14" t="n">
-        <v>0.321511834859848</v>
+        <v>0.6329904794692993</v>
       </c>
       <c r="F14" t="n">
-        <v>12.42500000000001</v>
+        <v>33.65909898477159</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03944444444444444</v>
+        <v>0.4122222222222222</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.1869918699186992</v>
       </c>
     </row>
     <row r="15">
@@ -1050,35 +1064,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2291666616753473</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4.667890487823795e-155</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3408587276935577</v>
+        <v>0.6338666677474976</v>
       </c>
       <c r="F15" t="n">
-        <v>12.42500000000001</v>
+        <v>43.09400000000002</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1428571428571428</v>
+        <v>1.152917505030181</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1891891891891892</v>
       </c>
     </row>
     <row r="16">
@@ -1091,35 +1107,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.3030302981165188</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>4.538023675136965e-155</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3275765478610992</v>
+        <v>0.6923012733459473</v>
       </c>
       <c r="F16" t="n">
-        <v>12.42500000000001</v>
+        <v>45.40473602484477</v>
       </c>
       <c r="G16" t="n">
-        <v>0.101283880171184</v>
+        <v>1.485021398002853</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3604651162790697</v>
       </c>
     </row>
     <row r="17">
@@ -1132,35 +1150,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.2734374950149536</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4.855515802897705e-155</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3282608687877655</v>
+        <v>0.6494925618171692</v>
       </c>
       <c r="F17" t="n">
-        <v>12.42500000000001</v>
+        <v>57.53275229357797</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09543010752688172</v>
+        <v>1.016129032258065</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="18">
@@ -1173,35 +1193,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.2664165065178871</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.01218206070194327</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3524843156337738</v>
+        <v>0.5802870392799377</v>
       </c>
       <c r="F18" t="n">
-        <v>12.42500000000001</v>
+        <v>40.71953706255169</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02764797507788162</v>
+        <v>0.3212616822429907</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="19">
@@ -1214,35 +1236,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1239436576949019</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2.925347354289179e-156</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3208551406860352</v>
+        <v>0.6064203381538391</v>
       </c>
       <c r="F19" t="n">
-        <v>12.42500000000001</v>
+        <v>12.76382636868556</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04680290046143705</v>
+        <v>0.5016479894528675</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="20">
@@ -1255,35 +1279,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008032128120514206</v>
+        <v>0.2621951181409875</v>
       </c>
       <c r="D20" t="n">
-        <v>1.21304235279905e-268</v>
+        <v>0.00301403069717324</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3401677906513214</v>
+        <v>0.6403802037239075</v>
       </c>
       <c r="F20" t="n">
-        <v>12.42500000000001</v>
+        <v>51.5761904761905</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05039034776437189</v>
+        <v>0.340667139815472</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="21">
@@ -1296,35 +1322,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.2048417082292481</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5.481377210324708e-79</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3378615379333496</v>
+        <v>0.5724970698356628</v>
       </c>
       <c r="F21" t="n">
-        <v>12.42500000000001</v>
+        <v>17.50437939648944</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04022662889518414</v>
+        <v>1.015864022662889</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.375</v>
+      </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0136986301369863</v>
+        <v>0.1798418972332016</v>
       </c>
     </row>
     <row r="22">
@@ -1337,35 +1365,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.3511450336110949</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.0422257144037985</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3471125662326813</v>
+        <v>0.6478288173675537</v>
       </c>
       <c r="F22" t="n">
-        <v>12.42500000000001</v>
+        <v>50.30096059479555</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04303030303030303</v>
+        <v>0.5218181818181818</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -1378,35 +1408,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005847952928251443</v>
+        <v>0.2934782561138023</v>
       </c>
       <c r="D23" t="n">
-        <v>1.811128572821972e-307</v>
+        <v>0.03211899636899531</v>
       </c>
       <c r="E23" t="n">
-        <v>0.351656973361969</v>
+        <v>0.6899160146713257</v>
       </c>
       <c r="F23" t="n">
-        <v>12.42500000000001</v>
+        <v>21.49396103896109</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03261368856224162</v>
+        <v>0.6306844281120808</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.452054794520548</v>
       </c>
     </row>
     <row r="24">
@@ -1419,35 +1451,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.282722508128615</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.02297004962446397</v>
       </c>
       <c r="E24" t="n">
-        <v>0.31206414103508</v>
+        <v>0.687569260597229</v>
       </c>
       <c r="F24" t="n">
-        <v>12.42500000000001</v>
+        <v>34.22731021897812</v>
       </c>
       <c r="G24" t="n">
-        <v>0.109062980030722</v>
+        <v>0.8878648233486943</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2481203007518797</v>
       </c>
     </row>
     <row r="25">
@@ -1460,35 +1494,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2222222172280665</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>9.21447839793583e-79</v>
       </c>
       <c r="E25" t="n">
-        <v>0.328554779291153</v>
+        <v>0.6143026351928711</v>
       </c>
       <c r="F25" t="n">
-        <v>12.42500000000001</v>
+        <v>37.50753846153847</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1070889894419306</v>
+        <v>0.9879336349924586</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="26">
@@ -1501,35 +1537,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.3017241330949019</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.04396547343484474</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3231311142444611</v>
+        <v>0.6827999353408813</v>
       </c>
       <c r="F26" t="n">
-        <v>12.42500000000001</v>
+        <v>36.28096491228075</v>
       </c>
       <c r="G26" t="n">
-        <v>0.123050259965338</v>
+        <v>1.441941074523397</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="27">
@@ -1542,35 +1580,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.3262411298010664</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.05266153951967517</v>
       </c>
       <c r="E27" t="n">
-        <v>0.311333566904068</v>
+        <v>0.6788228750228882</v>
       </c>
       <c r="F27" t="n">
-        <v>12.42500000000001</v>
+        <v>43.97398907103826</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09712722298221614</v>
+        <v>1.350205198358413</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4573643410852714</v>
       </c>
     </row>
     <row r="28">
@@ -1583,35 +1623,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.2377049130599974</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1.471774789060593e-78</v>
       </c>
       <c r="E28" t="n">
-        <v>0.327028751373291</v>
+        <v>0.6071135997772217</v>
       </c>
       <c r="F28" t="n">
-        <v>12.42500000000001</v>
+        <v>39.78727954971859</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1075757575757576</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2708333333333334</v>
       </c>
     </row>
     <row r="29">
@@ -1624,35 +1666,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.2901960737562476</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.0592866013047872</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3222382366657257</v>
+        <v>0.6490826606750488</v>
       </c>
       <c r="F29" t="n">
-        <v>12.42500000000001</v>
+        <v>39.5109523809524</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1232638888888889</v>
+        <v>1.670138888888889</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="30">
@@ -1665,35 +1709,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.06557376912523517</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1.532439586350152e-155</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4336258769035339</v>
+        <v>0.4118431806564331</v>
       </c>
       <c r="F30" t="n">
-        <v>12.42500000000001</v>
+        <v>24.00615384615386</v>
       </c>
       <c r="G30" t="n">
-        <v>0.71</v>
+        <v>7.56</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2592592592592593</v>
       </c>
     </row>
     <row r="31">
@@ -1706,35 +1752,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.07643311993833422</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>3.84611200391263e-79</v>
       </c>
       <c r="E31" t="n">
-        <v>0.415562242269516</v>
+        <v>0.4567783772945404</v>
       </c>
       <c r="F31" t="n">
-        <v>12.42500000000001</v>
+        <v>31.4866894920319</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6893203883495146</v>
+        <v>9.281553398058252</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2934782608695652</v>
       </c>
     </row>
     <row r="32">
@@ -1747,27 +1795,29 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.08080807915518828</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1.718497352464016e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4121761322021484</v>
+        <v>0.5366572737693787</v>
       </c>
       <c r="F32" t="n">
-        <v>12.42500000000001</v>
+        <v>44.33492537313433</v>
       </c>
       <c r="G32" t="n">
-        <v>0.71</v>
+        <v>5.67</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
@@ -1775,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="33">
@@ -1788,35 +1838,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.2285714243487348</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>8.174360191435212e-79</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3997314274311066</v>
+        <v>0.6225715279579163</v>
       </c>
       <c r="F33" t="n">
-        <v>12.42500000000001</v>
+        <v>60.31516129032258</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1966759002770083</v>
+        <v>2.227146814404432</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3922651933701657</v>
       </c>
     </row>
     <row r="34">
@@ -1829,35 +1881,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.1340782077975096</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>7.127627834060009e-156</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3917847871780396</v>
+        <v>0.5686533451080322</v>
       </c>
       <c r="F34" t="n">
-        <v>12.42500000000001</v>
+        <v>79.92010739260742</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1031976744186047</v>
+        <v>0.5930232558139535</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2198581560283688</v>
       </c>
     </row>
     <row r="35">
@@ -1870,35 +1924,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2754820887103947</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1.095283556166236e-78</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3391465246677399</v>
+        <v>0.6601959466934204</v>
       </c>
       <c r="F35" t="n">
-        <v>12.42500000000001</v>
+        <v>32.37386857707511</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06217162872154115</v>
+        <v>0.9483362521891419</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5061728395061729</v>
       </c>
     </row>
     <row r="36">
@@ -1911,35 +1967,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.3525179807150251</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.1008138137121011</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3042621910572052</v>
+        <v>0.6837273836135864</v>
       </c>
       <c r="F36" t="n">
-        <v>12.42500000000001</v>
+        <v>21.6464159663866</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1125198098256735</v>
+        <v>1.429477020602219</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3650793650793651</v>
       </c>
     </row>
     <row r="37">
@@ -1952,35 +2010,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.2658227798109278</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.02679810112637866</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3632136583328247</v>
+        <v>0.6643867492675781</v>
       </c>
       <c r="F37" t="n">
-        <v>12.42500000000001</v>
+        <v>46.95450657894739</v>
       </c>
       <c r="G37" t="n">
-        <v>0.07529162248144221</v>
+        <v>1.046659597030753</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.296875</v>
       </c>
     </row>
     <row r="38">
@@ -1993,35 +2053,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2343749955555556</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3.486477204714277e-155</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3629776239395142</v>
+        <v>0.6037901043891907</v>
       </c>
       <c r="F38" t="n">
-        <v>12.42500000000001</v>
+        <v>43.47345242874351</v>
       </c>
       <c r="G38" t="n">
-        <v>0.09184993531694696</v>
+        <v>2.046571798188875</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.4630872483221477</v>
       </c>
     </row>
     <row r="39">
@@ -2034,35 +2096,37 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.2752293527985861</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1.832451436723792e-78</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3317360877990723</v>
+        <v>0.6696382761001587</v>
       </c>
       <c r="F39" t="n">
-        <v>12.42500000000001</v>
+        <v>47.30111111111111</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1047197640117994</v>
+        <v>0.9557522123893806</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.2537313432835821</v>
       </c>
     </row>
     <row r="40">
@@ -2075,35 +2139,37 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.1746724846780192</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2.580419168612744e-79</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2874237596988678</v>
+        <v>0.5894784331321716</v>
       </c>
       <c r="F40" t="n">
-        <v>12.42500000000001</v>
+        <v>20.53999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07819383259911894</v>
+        <v>0.5870044052863436</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1954022988505747</v>
       </c>
     </row>
     <row r="41">
@@ -2116,35 +2182,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.2897862184914326</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.0350380279479637</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2836160659790039</v>
+        <v>0.6345568299293518</v>
       </c>
       <c r="F41" t="n">
-        <v>12.42500000000001</v>
+        <v>41.71002870813399</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04869684499314129</v>
+        <v>0.7167352537722909</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4214876033057851</v>
       </c>
     </row>
     <row r="42">
@@ -2157,35 +2225,37 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.3312499950125001</v>
       </c>
       <c r="D42" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>0.07159434395621361</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3234778940677643</v>
+        <v>0.6125738024711609</v>
       </c>
       <c r="F42" t="n">
-        <v>12.42500000000001</v>
+        <v>36.23093034825871</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08114285714285714</v>
+        <v>1.108571428571429</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="43">
@@ -2198,27 +2268,29 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2092457372416693</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>7.720294295067779e-79</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3453939259052277</v>
+        <v>0.6243157386779785</v>
       </c>
       <c r="F43" t="n">
-        <v>12.42500000000001</v>
+        <v>43.59220562521858</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06580166821130677</v>
+        <v>1.409638554216867</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -2226,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.2068965517241379</v>
       </c>
     </row>
     <row r="44">
@@ -2239,35 +2311,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.305084740833094</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.08314225201959277</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3232988715171814</v>
+        <v>0.7096904516220093</v>
       </c>
       <c r="F44" t="n">
-        <v>12.42500000000001</v>
+        <v>41.86318027210888</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08151549942594719</v>
+        <v>0.8450057405281286</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="45">
@@ -2280,35 +2354,37 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3110465078490063</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.005103509945044678</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3477978110313416</v>
+        <v>0.6566540002822876</v>
       </c>
       <c r="F45" t="n">
-        <v>12.42500000000001</v>
+        <v>36.17792679532383</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01946805593638607</v>
+        <v>0.291746641074856</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="46">
@@ -2321,35 +2397,37 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3575832261797935</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.0536133482139747</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3389484584331512</v>
+        <v>0.6485623717308044</v>
       </c>
       <c r="F46" t="n">
-        <v>12.42500000000001</v>
+        <v>52.06540000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01966214345056771</v>
+        <v>0.4536139573525339</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5294117647058824</v>
       </c>
     </row>
     <row r="47">
@@ -2362,35 +2440,37 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3047285419460743</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.0102075187239391</v>
       </c>
       <c r="E47" t="n">
-        <v>0.355352520942688</v>
+        <v>0.6858015060424805</v>
       </c>
       <c r="F47" t="n">
-        <v>12.42500000000001</v>
+        <v>45.42803529937444</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0282981267437226</v>
+        <v>0.4591470705460343</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3396226415094339</v>
       </c>
     </row>
     <row r="48">
@@ -2403,35 +2483,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.3212851363210271</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1.793415263450387e-78</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3648593723773956</v>
+        <v>0.660669207572937</v>
       </c>
       <c r="F48" t="n">
-        <v>12.42500000000001</v>
+        <v>43.20929472477067</v>
       </c>
       <c r="G48" t="n">
-        <v>0.15203426124197</v>
+        <v>2.366167023554604</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3006993006993007</v>
       </c>
     </row>
     <row r="49">
@@ -2444,35 +2526,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.28971962132588</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>0.09626501273837079</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3483927845954895</v>
+        <v>0.6747770309448242</v>
       </c>
       <c r="F49" t="n">
-        <v>12.42500000000001</v>
+        <v>47.16046008869179</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1368015414258189</v>
+        <v>1.529865125240848</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="50">
@@ -2485,35 +2569,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.3140495821487604</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.06696488702256605</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3485001027584076</v>
+        <v>0.6648523211479187</v>
       </c>
       <c r="F50" t="n">
-        <v>12.42500000000001</v>
+        <v>50.17734363957601</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1360153256704981</v>
+        <v>1.808429118773946</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3081761006289309</v>
       </c>
     </row>
     <row r="51">
@@ -2526,35 +2612,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.2549800746832591</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.01998383402256366</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3496768474578857</v>
+        <v>0.6231213808059692</v>
       </c>
       <c r="F51" t="n">
-        <v>12.42500000000001</v>
+        <v>49.0663247863248</v>
       </c>
       <c r="G51" t="n">
-        <v>0.09454061251664447</v>
+        <v>1.013315579227696</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3037974683544303</v>
       </c>
     </row>
     <row r="52">
@@ -2567,35 +2655,37 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.008403360933196829</v>
+        <v>0.284403664748443</v>
       </c>
       <c r="D52" t="n">
-        <v>2.960553565183628e-265</v>
+        <v>0.05948998861904049</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3448955118656158</v>
+        <v>0.6435996890068054</v>
       </c>
       <c r="F52" t="n">
-        <v>12.42500000000001</v>
+        <v>47.99539473684212</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05148658448150834</v>
+        <v>0.8491660623640319</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="53">
@@ -2608,35 +2698,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.3967611287619041</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.05533567025204253</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3169403970241547</v>
+        <v>0.6603667736053467</v>
       </c>
       <c r="F53" t="n">
-        <v>12.42500000000001</v>
+        <v>46.06323066311484</v>
       </c>
       <c r="G53" t="n">
-        <v>0.03788687299893276</v>
+        <v>0.6840981856990395</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.3989071038251367</v>
       </c>
     </row>
     <row r="54">
@@ -2649,35 +2741,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.1806853536933843</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1.106369304663641e-79</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3199907243251801</v>
+        <v>0.5802265405654907</v>
       </c>
       <c r="F54" t="n">
-        <v>12.42500000000001</v>
+        <v>4.446921052631581</v>
       </c>
       <c r="G54" t="n">
-        <v>0.05224429727740986</v>
+        <v>0.5261221486387049</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2631578947368421</v>
       </c>
     </row>
     <row r="55">
@@ -2690,35 +2784,37 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.1873278191258947</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2.97480157371679e-156</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3372025191783905</v>
+        <v>0.6448232531547546</v>
       </c>
       <c r="F55" t="n">
-        <v>12.42500000000001</v>
+        <v>-8.512272727272716</v>
       </c>
       <c r="G55" t="n">
-        <v>0.04592496765847348</v>
+        <v>0.5413971539456662</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2660550458715596</v>
       </c>
     </row>
     <row r="56">
@@ -2731,35 +2827,37 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.1328671305628637</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>2.563874517638037e-160</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3237845599651337</v>
+        <v>0.5497390627861023</v>
       </c>
       <c r="F56" t="n">
-        <v>12.42500000000001</v>
+        <v>13.01000000000002</v>
       </c>
       <c r="G56" t="n">
-        <v>0.04530950861518826</v>
+        <v>0.167836630504148</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1366906474820144</v>
       </c>
     </row>
     <row r="57">
@@ -2772,27 +2870,29 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.3036809773184915</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.01404256187110488</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3658333718776703</v>
+        <v>0.6289132833480835</v>
       </c>
       <c r="F57" t="n">
-        <v>12.42500000000001</v>
+        <v>36.39327595976769</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02446588559614059</v>
+        <v>0.439696760854583</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.75</v>
+      </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
@@ -2800,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.3457943925233645</v>
       </c>
     </row>
     <row r="58">
@@ -2813,27 +2913,29 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.0120481921868196</v>
+        <v>0.1948051898155255</v>
       </c>
       <c r="D58" t="n">
-        <v>3.542014107114671e-257</v>
+        <v>2.237708954721772e-155</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3401473164558411</v>
+        <v>0.6211922168731689</v>
       </c>
       <c r="F58" t="n">
-        <v>12.42500000000001</v>
+        <v>29.02977272727276</v>
       </c>
       <c r="G58" t="n">
-        <v>0.07667386609071274</v>
+        <v>0.9600431965442765</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
@@ -2841,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2929292929292929</v>
       </c>
     </row>
     <row r="59">
@@ -2854,35 +2956,37 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.1653543257089716</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>2.838187488406426e-155</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3623087108135223</v>
+        <v>0.5985031723976135</v>
       </c>
       <c r="F59" t="n">
-        <v>12.42500000000001</v>
+        <v>33.96565725413831</v>
       </c>
       <c r="G59" t="n">
-        <v>0.08964646464646464</v>
+        <v>1.069444444444444</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3247588424437299</v>
       </c>
     </row>
     <row r="60">
@@ -2895,35 +2999,37 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.00446428549356267</v>
+        <v>0.2097488876478688</v>
       </c>
       <c r="D60" t="n">
-        <v>8.265132997605698e-314</v>
+        <v>6.701069466588682e-79</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3443799018859863</v>
+        <v>0.6065818667411804</v>
       </c>
       <c r="F60" t="n">
-        <v>12.42500000000001</v>
+        <v>17.16231223328592</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02480782669461915</v>
+        <v>0.6044723969252271</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.6449704142011834</v>
       </c>
     </row>
     <row r="61">
@@ -2936,35 +3042,37 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.164179101085988</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>2.866303580341867e-155</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3938581645488739</v>
+        <v>0.4843451082706451</v>
       </c>
       <c r="F61" t="n">
-        <v>12.42500000000001</v>
+        <v>36.32344477711246</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2874493927125506</v>
+        <v>2.566801619433198</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.2361111111111111</v>
       </c>
     </row>
     <row r="62">
@@ -2977,35 +3085,37 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.1954022939800504</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>2.347352468170902e-155</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3285914063453674</v>
+        <v>0.6310755610466003</v>
       </c>
       <c r="F62" t="n">
-        <v>12.42500000000001</v>
+        <v>44.10227272727275</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1775</v>
+        <v>1.6825</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2972972972972973</v>
       </c>
     </row>
     <row r="63">
@@ -3018,35 +3128,37 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.1935483821076298</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>4.056133394799789e-155</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3153927028179169</v>
+        <v>0.610514760017395</v>
       </c>
       <c r="F63" t="n">
-        <v>12.42500000000001</v>
+        <v>31.35618096093398</v>
       </c>
       <c r="G63" t="n">
-        <v>0.09902370990237098</v>
+        <v>1.329149232914923</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="64">
@@ -3059,35 +3171,37 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.2558139485968392</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>0.02276131568187345</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3128878772258759</v>
+        <v>0.6663359999656677</v>
       </c>
       <c r="F64" t="n">
-        <v>12.42500000000001</v>
+        <v>48.02504477611942</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1163934426229508</v>
+        <v>1.529508196721312</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="65">
@@ -3100,35 +3214,37 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>0.2258064469055672</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>0.03765353702274584</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3203713893890381</v>
+        <v>0.6130156517028809</v>
       </c>
       <c r="F65" t="n">
-        <v>12.42500000000001</v>
+        <v>43.88668421052634</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1422845691382766</v>
+        <v>1.985971943887776</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3893129770992366</v>
       </c>
     </row>
     <row r="66">
@@ -3141,35 +3257,37 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.317689525709445</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.06955516989406148</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3236204087734222</v>
+        <v>0.7091745734214783</v>
       </c>
       <c r="F66" t="n">
-        <v>12.42500000000001</v>
+        <v>52.41036585365856</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0890840652446675</v>
+        <v>1.023839397741531</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3023255813953489</v>
       </c>
     </row>
     <row r="67">
@@ -3182,35 +3300,37 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.2886597888867633</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>0.1058330858114581</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3227953910827637</v>
+        <v>0.6811655163764954</v>
       </c>
       <c r="F67" t="n">
-        <v>12.42500000000001</v>
+        <v>51.26584028356964</v>
       </c>
       <c r="G67" t="n">
-        <v>0.09726027397260274</v>
+        <v>1.372602739726027</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3548387096774193</v>
       </c>
     </row>
     <row r="68">
@@ -3223,35 +3343,37 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.1149425271601268</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>4.394841927100256e-79</v>
       </c>
       <c r="E68" t="n">
-        <v>0.3923715353012085</v>
+        <v>0.4836772084236145</v>
       </c>
       <c r="F68" t="n">
-        <v>12.42500000000001</v>
+        <v>40.11654729956393</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5590551181102362</v>
+        <v>7.637795275590551</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3706293706293706</v>
       </c>
     </row>
   </sheetData>
